--- a/마켓센싱 정보수집 계층 통합.xlsx
+++ b/마켓센싱 정보수집 계층 통합.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="참고사이트" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검색어" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수집자동화 설계(초안)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="소스별 수집방식(초안)" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4317,4 +4318,3308 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>소스별 수집방식 (초안) — 14개 그룹 아래 전체 소스 펼침 · ※ 값은 담당자와 하나씩 확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>기본축</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>그룹</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>소스명</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>제공기관 / URL</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>유형(출처)</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>수집방식(초안)</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>접근·권한</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>자동화(초안)</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>사람 개입점</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>확인 메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>❶ 공공·정책</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>범죄·안전 통계</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>경찰청 범죄통계/범죄분석</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.police.go.kr</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>발간 통계 다운로드 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>부분(발간주기)</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>수치 추출·해석</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>❶ 공공·정책</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>범죄·안전 통계</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>대검찰청 범죄분석</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.spo.go.kr</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>발간 통계 다운로드 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>부분(발간주기)</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>수치 추출·해석</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>❶ 공공·정책</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>범죄·안전 통계</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>소방청 / 행정안전부</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.nfa.go.kr / https://www.mois.go.kr</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>발간 통계 다운로드 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>부분(발간주기)</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>수치 추출·해석</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>❶ 공공·정책</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>범죄·안전 통계</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>고용노동부</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.moel.go.kr</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>발간 통계 다운로드 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>부분(발간주기)</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>수치 추출·해석</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>❶ 공공·정책</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>범죄·안전 통계</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>통계청 KOSIS</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>https://kosis.kr</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>발간 통계 다운로드 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>부분(발간주기)</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>수치 추출·해석</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>❶ 공공·정책</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>범죄·안전 통계</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>前年 사건사고 통계 종합 분석</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>경찰청·소방청·가스공사 등</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>발간보고서</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>발간 통계 다운로드 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>부분(발간주기)</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>수치 추출·해석</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>❶ 공공·정책</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>범죄·안전 통계</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>인구주택총조사 결과</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>통계청</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>발간보고서</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>발간 통계 다운로드 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>부분(발간주기)</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>수치 추출·해석</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>❶ 공공·정책</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>범죄·안전 통계</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>교통사고 통계 분석</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>도로교통공단</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>발간보고서</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>발간 통계 다운로드 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>부분(발간주기)</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>수치 추출·해석</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>❶ 공공·정책</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>법령·입법</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>국가법령정보센터</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.law.go.kr</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>크롤링 / 입법예고 RSS</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>해당 여부 판단</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>❶ 공공·정책</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>법령·입법</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>국민참여입법센터</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>https://opinion.lawmaking.go.kr</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>크롤링 / 입법예고 RSS</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>해당 여부 판단</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>❶ 공공·정책</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>법령·입법</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>정부입법지원센터</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.lawmaking.go.kr</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>크롤링 / 입법예고 RSS</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>해당 여부 판단</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>❶ 공공·정책</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>정책·공공</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>정책브리핑</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>https://www.korea.kr</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>크롤링 + 공공데이터 API(KOSIS)</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>주제 관련성 선별</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>❶ 공공·정책</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>정책·공공</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>소상공인시장진흥공단</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>https://www.semas.or.kr</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>크롤링 + 공공데이터 API(KOSIS)</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>주제 관련성 선별</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>❶ 공공·정책</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>정책·공공</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>중소기업연구원</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kosi.re.kr</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>크롤링 + 공공데이터 API(KOSIS)</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>주제 관련성 선별</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>❶ 공공·정책</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>정책·공공</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>협동조합</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.coop.go.kr</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>크롤링 + 공공데이터 API(KOSIS)</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>주제 관련성 선별</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>❶ 공공·정책</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>정책·공공</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>국가통계포털(KOSIS)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>https://kosis.kr</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>크롤링 + 공공데이터 API(KOSIS)</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>주제 관련성 선별</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>❶ 공공·정책</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>정책·공공</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>이렇게 달라집니다.</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>https://whatsnew.moef.go.kr/mec/ots/dif/main.do</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>크롤링 + 공공데이터 API(KOSIS)</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>주제 관련성 선별</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>❶ 공공·정책</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>정책·공공</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>정부24</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gov.kr</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>크롤링 + 공공데이터 API(KOSIS)</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>주제 관련성 선별</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>❶ 공공·정책</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>정책·규제 보고서</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>국가정보보호백서</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>한국인터넷진흥원(KISA)</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>발간보고서</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>보도자료 모니터링 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>당사 영향 판단</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>❶ 공공·정책</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>정책·규제 보고서</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>정보보호/물리보안 기술 규제·국가 R&amp;D 과제</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>과기정통부·한국인터넷진흥원</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>발간보고서</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>보도자료 모니터링 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>당사 영향 판단</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>❶ 공공·정책</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>정책·규제 보고서</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>개인정보·생체인식 가이드라인/규제 법령</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>개인정보보호위원회</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>발간보고서</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>보도자료 모니터링 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>당사 영향 판단</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>❶ 공공·정책</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>정책·규제 보고서</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>지자체 도시안전망·사회안전망 구축사업</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>행정안전부</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>발간보고서</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>보도자료 모니터링 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>당사 영향 판단</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>❶ 공공·정책</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>정책·규제 보고서</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>종합 법안 모니터링</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>의안정보시스템</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>발간보고서</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>보도자료 모니터링 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>당사 영향 판단</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>❶ 공공·정책</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>정책·규제 보고서</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>정부 부처별 공식 보도자료 모니터링</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>대한민국 정책브리핑</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>발간보고서</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>보도자료 모니터링 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>당사 영향 판단</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>❷ 미디어·뉴스</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>검색어 기반</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>키워드 57종(경쟁사·글로벌·업계·마케팅)</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>검색어 시트 참조</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>검색어</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>키워드 검색 크롤링</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>키워드 유지·선별</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>❷ 미디어·뉴스</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>보안·안전 전문지</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>보안뉴스</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>https://www.boannews.com</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>크롤링 / RSS</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>기사 선별</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>❷ 미디어·뉴스</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>보안·안전 전문지</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>시큐리티월드</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>https://www.securityworld.co.kr</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>크롤링 / RSS</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>기사 선별</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>❷ 미디어·뉴스</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>보안·안전 전문지</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>세이프타임즈</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>https://www.safetimes.co.kr</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>크롤링 / RSS</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>기사 선별</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>❷ 미디어·뉴스</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>일반 언론·포털(신문스크랩)</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>커뮤니케이션팀 신문스크랩·사업부 '오늘의 시장동향'</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>사내 메일링/포털</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>업무순서</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>검색 크롤링 / 뉴스 API</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>공개(일부 제휴)</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>선별</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>경제·금융 연구</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>KDI경제동향</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kdi.re.kr/research/monTrends</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>발간물 다운로드 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>부분(발간주기)</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>핵심 수치 추출</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>경제·금융 연구</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>KB경영연구소</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kbfg.com/kbresearch/index.do</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>발간물 다운로드 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>부분(발간주기)</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>핵심 수치 추출</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>경제·금융 연구</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>KB Think</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>https://kbthink.com/main.html</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>발간물 다운로드 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>부분(발간주기)</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>핵심 수치 추출</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>경제·금융 연구</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>한국은행(소비자동향)</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>https://www.bok.or.kr</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>발간물 다운로드 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>부분(발간주기)</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>핵심 수치 추출</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>기술·R&amp;D</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>기술정보진흥센터</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tipa.or.kr</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>이메일 구독 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>요약·선별</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>기술·R&amp;D</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>ITFIND(정보통신기획평가원)</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>https://www.itfind.or.kr</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>이메일 구독 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>요약·선별</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>기술·R&amp;D</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>KISDI(정보통신정책연구원)</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kisdi.re.kr</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>이메일 구독 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>요약·선별</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>보안산업·협회</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>한국보안산업협회(KSIA)</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksia.or.kr</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>연차보고서 다운로드</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>공개(일부 회원)</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>어려움(수동)</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>수치 확보</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>보안산업·협회</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>SIA(Security Industry Association)</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>https://www.securityindustry.org</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>연차보고서 다운로드</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>공개(일부 회원)</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>어려움(수동)</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>수치 확보</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>보안산업·협회</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>KISIA(한국정보보호산업협회)</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kisia.or.kr</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>연차보고서 다운로드</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>공개(일부 회원)</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>어려움(수동)</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>수치 확보</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>위협 인텔리전스</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>안랩 ASEC / SK쉴더스 EQST 리포트</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>각사 홈페이지</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>리포트 다운로드 / RSS</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>위협 판단</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>위협 인텔리전스</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>KISA(한국인터넷진흥원)</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>리포트 다운로드 / RSS</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>위협 판단</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>정기 발간보고서</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>세계 전망 보고서</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>국제통화기금(IMF)</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>발간보고서</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>발간 알림 + 다운로드</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>공개(트렌드코리아=유료 도서)</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>수치·시사점 도출</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>정기 발간보고서</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>경제 전망 보고서(分期)</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>한국은행</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>발간보고서</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>발간 알림 + 다운로드</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>공개(트렌드코리아=유료 도서)</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>수치·시사점 도출</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>정기 발간보고서</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>지역경제보고서</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>한국은행</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>발간보고서</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>발간 알림 + 다운로드</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>공개(트렌드코리아=유료 도서)</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>수치·시사점 도출</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>정기 발간보고서</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>경제∙산업 전망 보고서(半期)</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>산업연구원(KIET)</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>발간보고서</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>발간 알림 + 다운로드</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>공개(트렌드코리아=유료 도서)</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>수치·시사점 도출</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>정기 발간보고서</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>KDI 경제동향 및 전망</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>한국개발연구원(KDI)</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>발간보고서</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>발간 알림 + 다운로드</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>공개(트렌드코리아=유료 도서)</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>수치·시사점 도출</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>정기 발간보고서</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>AI 브리프</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>소프트웨어정책연구소(SPRi)</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>발간보고서</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>발간 알림 + 다운로드</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>공개(트렌드코리아=유료 도서)</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>수치·시사점 도출</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>정기 발간보고서</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>이슈리포트</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>소프트웨어정책연구소(SPRi)</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>발간보고서</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>발간 알림 + 다운로드</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>공개(트렌드코리아=유료 도서)</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>수치·시사점 도출</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>정기 발간보고서</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>국내외 보안시장 전망 보고서</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>보안뉴스/시큐리티월드</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>발간보고서</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>발간 알림 + 다운로드</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>공개(트렌드코리아=유료 도서)</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>수치·시사점 도출</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>정기 발간보고서</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>(국내) 정보보호산업 실태조사 결과</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>한국정보보호산업협회(KISIA)</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>발간보고서</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>발간 알림 + 다운로드</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>공개(트렌드코리아=유료 도서)</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>수치·시사점 도출</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>정기 발간보고서</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>무인경비 M/S 조사 결과</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>한국갤럽</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>발간보고서</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>발간 알림 + 다운로드</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>공개(트렌드코리아=유료 도서)</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>수치·시사점 도출</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>정기 발간보고서</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>브랜드파워(K-BPI) 조사 결과</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>한국능률협회컨설팅(KMAC)</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>발간보고서</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>발간 알림 + 다운로드</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>공개(트렌드코리아=유료 도서)</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>수치·시사점 도출</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>정기 발간보고서</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>국가고객만족도(NCSI) 조사 결과</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>한국생산성본부(KPC)</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>발간보고서</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>발간 알림 + 다운로드</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>공개(트렌드코리아=유료 도서)</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>수치·시사점 도출</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>정기 발간보고서</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>한국서비스품질지수(KS-SQI) 조사 결과</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>한국표준협회(KSA)</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>발간보고서</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>발간 알림 + 다운로드</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>공개(트렌드코리아=유료 도서)</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>수치·시사점 도출</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>정기 발간보고서</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>고객만족도(KCSI) 조사 결과</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>한국능률협회컨설팅(KMAC)</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>발간보고서</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>발간 알림 + 다운로드</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>공개(트렌드코리아=유료 도서)</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>수치·시사점 도출</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>❸ 연구·전문보고서</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>정기 발간보고서</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>트렌드 코리아</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>서울대 소비트렌드 분석센터</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>발간보고서</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>발간 알림 + 다운로드</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>공개(트렌드코리아=유료 도서)</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>수치·시사점 도출</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>❹ 국내외 기술전</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>국내외 기술전(전시회)</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>CES</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>미국 라스베이거스</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>기술전시회</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>공식 사이트·기사 크롤링</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>부분(연 1회)</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>시사점 정리</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>❹ 국내외 기술전</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>국내외 기술전(전시회)</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>MWC</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>스페인 바르셀로나</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>기술전시회</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>공식 사이트·기사 크롤링</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>부분(연 1회)</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>시사점 정리</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>❹ 국내외 기술전</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>국내외 기술전(전시회)</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>ISC WEST</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>미국 라스베이거스</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>기술전시회</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>공식 사이트·기사 크롤링</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>부분(연 1회)</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>시사점 정리</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>❹ 국내외 기술전</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>국내외 기술전(전시회)</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>IFA</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>독일 베를린</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>기술전시회</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>공식 사이트·기사 크롤링</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>부분(연 1회)</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>시사점 정리</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>❺ 트렌드 뉴스레터</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>트렌드·마케팅</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>더외식</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>https://www.atfis.or.kr</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>이메일 뉴스레터 수신 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>공개(일부 로그인/유료)</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>주제 선별</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>❺ 트렌드 뉴스레터</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>트렌드·마케팅</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>네이버 데이터랩</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>https://datalab.naver.com</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>이메일 뉴스레터 수신 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>공개(일부 로그인/유료)</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>주제 선별</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>❺ 트렌드 뉴스레터</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>트렌드·마케팅</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>SK스퀘어 데이터랩</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>https://incross.com</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>이메일 뉴스레터 수신 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>공개(일부 로그인/유료)</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>주제 선별</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>❺ 트렌드 뉴스레터</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>트렌드·마케팅</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>캐릿(Careet)</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>https://www.careet.net</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>이메일 뉴스레터 수신 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>공개(일부 로그인/유료)</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>주제 선별</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>❺ 트렌드 뉴스레터</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>트렌드·마케팅</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>나스미디어(KT)</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>https://www.nasmedia.co.kr</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>이메일 뉴스레터 수신 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>공개(일부 로그인/유료)</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>주제 선별</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>❺ 트렌드 뉴스레터</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>트렌드·마케팅</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>CJ메조미디어</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cjmezzomedia.com/insight-m</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>이메일 뉴스레터 수신 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>공개(일부 로그인/유료)</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>주제 선별</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>❺ 트렌드 뉴스레터</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>트렌드·마케팅</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>엠브레인</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>https://www.trendmonitor.co.kr</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>참고사이트</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>이메일 뉴스레터 수신 + 크롤링</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>공개(일부 로그인/유료)</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>주제 선별</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/마켓센싱 정보수집 계층 통합.xlsx
+++ b/마켓센싱 정보수집 계층 통합.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검색어" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수집자동화 설계(초안)" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="소스별 수집방식(초안)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수집 스케줄" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -91,7 +92,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -113,11 +114,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -141,6 +186,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -666,9 +713,9 @@
           <t>※ 출처: PI Portal [E2E 과제현황 #4] · N-ERP To-Be 프로세스 체계도</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
+      <c r="B10" s="11" t="n"/>
+      <c r="C10" s="11" t="n"/>
+      <c r="D10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -1121,8 +1168,8 @@
 · 당사 영업확대 기회가 있는 정책·시장·사회이슈 소개</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4326,7 +4373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4339,6 +4386,8 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4399,6 +4448,16 @@
           <t>확인 메모</t>
         </is>
       </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>자동화 등급</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>검증(방식)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -4447,6 +4506,16 @@
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr"/>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -4495,6 +4564,16 @@
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -4543,6 +4622,16 @@
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -4591,6 +4680,16 @@
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -4639,6 +4738,16 @@
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>1순위</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>✅ OpenAPI</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -4687,6 +4796,16 @@
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -4735,6 +4854,16 @@
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -4783,6 +4912,16 @@
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -4831,6 +4970,16 @@
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>1순위</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>✅ OpenAPI</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -4879,6 +5028,16 @@
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -4927,6 +5086,16 @@
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -4975,6 +5144,16 @@
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>1순위</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>✅ RSS</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -5023,6 +5202,16 @@
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -5071,6 +5260,16 @@
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -5119,6 +5318,16 @@
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -5167,6 +5376,16 @@
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>1순위</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>✅ OpenAPI</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -5215,6 +5434,16 @@
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -5263,6 +5492,16 @@
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -5311,6 +5550,16 @@
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -5359,6 +5608,16 @@
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -5407,6 +5666,16 @@
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -5455,6 +5724,16 @@
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -5503,6 +5782,16 @@
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -5551,6 +5840,16 @@
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -5599,6 +5898,16 @@
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>1순위</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>✅ 경로A(웹검색)+빅카인즈</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -5647,6 +5956,16 @@
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>1순위</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>✅ RSS</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -5695,6 +6014,16 @@
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>1순위</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>✅ 보안뉴스와 동일(RSS)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -5743,6 +6072,16 @@
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -5791,6 +6130,16 @@
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>후순위</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>🔒 사내(방식 보류)+빅카인즈 보강</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -5839,6 +6188,16 @@
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>🔶 캘린더 크롤+PDF</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -5887,6 +6246,16 @@
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>🔶 캘린더 크롤+PDF</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -5935,6 +6304,16 @@
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>🔶 캘린더 크롤+PDF</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -5983,6 +6362,16 @@
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>🔶 캘린더 크롤+PDF</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -6031,6 +6420,16 @@
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>🔶 캘린더 크롤+PDF</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -6079,6 +6478,16 @@
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr"/>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>🔶 캘린더 크롤+PDF</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -6127,6 +6536,16 @@
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr"/>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>🔶 캘린더 크롤+PDF</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -6175,6 +6594,16 @@
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr"/>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>후순위</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>🔒 연차·일부 회원제</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -6223,6 +6652,16 @@
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>후순위</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>🔒 연차·일부 회원제</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -6271,6 +6710,16 @@
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr"/>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>후순위</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>🔒 연차·일부 회원제</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -6319,6 +6768,16 @@
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>🔶 캘린더 크롤+PDF</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -6367,6 +6826,16 @@
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr"/>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>🔶 캘린더 크롤+PDF</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -6415,6 +6884,16 @@
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr"/>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>🔶 캘린더 크롤+PDF</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -6463,6 +6942,16 @@
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr"/>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>🔶 캘린더 크롤+PDF</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -6511,6 +7000,16 @@
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>🔶 캘린더 크롤+PDF</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -6559,6 +7058,16 @@
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr"/>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>🔶 캘린더 크롤+PDF</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -6607,6 +7116,16 @@
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr"/>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>🔶 캘린더 크롤+PDF</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -6655,6 +7174,16 @@
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr"/>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>🔶 캘린더 크롤+PDF</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -6703,6 +7232,16 @@
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr"/>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>🔶 캘린더 크롤+PDF</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -6751,6 +7290,16 @@
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr"/>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>🔶 캘린더 크롤+PDF</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -6799,6 +7348,16 @@
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr"/>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>🔶 캘린더 크롤+PDF</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -6847,6 +7406,16 @@
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr"/>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>🔶 캘린더 크롤+PDF</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -6895,6 +7464,16 @@
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr"/>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>🔶 캘린더 크롤+PDF</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -6943,6 +7522,16 @@
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr"/>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>🔶 캘린더 크롤+PDF</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -6991,6 +7580,16 @@
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr"/>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>🔶 캘린더 크롤+PDF</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -7039,6 +7638,16 @@
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr"/>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>🔶 캘린더 크롤+PDF</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -7087,6 +7696,16 @@
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr"/>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>🔶 캘린더 크롤+PDF</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -7135,6 +7754,16 @@
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr"/>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>🔶 경로A+개최월 캘린더</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -7183,6 +7812,16 @@
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr"/>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>🔶 경로A+개최월 캘린더</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -7231,6 +7870,16 @@
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr"/>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>🔶 경로A+개최월 캘린더</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -7279,6 +7928,16 @@
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr"/>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>🔶 경로A+개최월 캘린더</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -7327,6 +7986,16 @@
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr"/>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -7375,6 +8044,16 @@
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr"/>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>1순위</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>✅ OpenAPI</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -7423,6 +8102,16 @@
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr"/>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -7471,6 +8160,16 @@
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr"/>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>후순위</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>🔒 유료/로그인</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -7519,6 +8218,16 @@
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr"/>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -7567,6 +8276,16 @@
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr"/>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>🔶 크롤(공개)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -7615,11 +8334,364 @@
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr"/>
-    </row>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>후순위</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>🔒 유료/로그인</t>
+        </is>
+      </c>
+    </row>
+    <row r="70"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>수집 스케줄 (캘린더) — 대시보드 '수집 캘린더' 메뉴 후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>주기 / 월</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>수집 항목</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>category(10대)</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>상시(매일)</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>경로A 키워드 웹검색+빅카인즈 · RSS(정책브리핑·보안뉴스) · 입법예고 · 네이버데이터랩</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>자동</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>매월 초</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>KDI 경제동향 · SPRi AI브리프 · 이슈리포트</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>8·5</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>자동/반자동</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>매월 하순</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>한국은행 BSI·ESI</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>9. 경제지표</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>★ 필수(현행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>1월</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>CES · IMF 세계경제전망 · 前年 사건사고 통계</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>5·8·6</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2월</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>MWC(~3월) · 경제전망(분기,한은) · 국내외 보안시장 전망★ · 정보보호 실태조사(~3월)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>5·8·1·7</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>★ 보안시장 전망</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>3월</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>MWC · ISC WEST(~4월) · 브랜드파워 K-BPI</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>5·1·3</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>4월</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>ISC WEST · IMF 세계경제전망</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>1·8</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>5월</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>국가고객만족도 NCSI · 경제전망(분기) · 경제·산업전망(반기,KIET)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>3·8</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>6월</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>국가정보보호백서(KISA)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>7월</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>서비스품질 KS-SQI · 인구주택총조사 · IMF 세계경제전망</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>3·6·8</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>8월</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>경제전망(분기) · 경찰청 범죄통계(8월경)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>8·6</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>9월</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>IFA · 정보보호산업 실태조사★(KISIA) · 고객만족도 KCSI</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>5·1·3</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>★ 정보보호산업 실태조사</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>10월</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>트렌드 코리아 · IMF 세계경제전망</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>6·8</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>11월</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>경제전망(분기) · 경제·산업전망(반기) · 교통사고 통계 · 무인경비 M/S</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>8·6·3</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>12월</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>(11월말 분기 경제전망 이월 확인)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>